--- a/comment.xlsx
+++ b/comment.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/ファイル名変更セット/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{481E7213-C6EC-44B2-B096-9C537337E363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B69D9BA7-1D4F-424F-90E7-D88E0D2D69FD}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{481E7213-C6EC-44B2-B096-9C537337E363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B733C6B-10CA-4775-9341-A33987CFA5A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C99B29C7-3A4C-4F85-8138-E5477A2FBA29}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C99B29C7-3A4C-4F85-8138-E5477A2FBA29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="162">
   <si>
     <t>品番</t>
     <rPh sb="0" eb="2">
@@ -1290,6 +1290,58 @@
   </si>
   <si>
     <t>No781</t>
+  </si>
+  <si>
+    <t>MC03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIF期間限定品2015/8/7～9/30</t>
+    <rPh sb="3" eb="7">
+      <t>キカンゲンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>丸文木工（廃業）にて製作</t>
+    <rPh sb="0" eb="1">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>モッコウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ハイギョウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>張替は特注作業依頼書にて要見積もり</t>
+    <rPh sb="0" eb="2">
+      <t>ハリカエ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トクチュウ</t>
+    </rPh>
+    <rPh sb="5" eb="10">
+      <t>サギョウイライショ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1462,6 +1514,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1761,20 +1817,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F89E10-74DD-4645-9643-023642A8D72D}">
-  <dimension ref="A1:L54"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L55"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.9140625" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.8984375" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="14.4140625" customWidth="1"/>
-    <col min="5" max="5" width="16.4140625" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.25" customWidth="1"/>
-    <col min="8" max="8" width="11.08203125" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" customWidth="1"/>
+    <col min="6" max="6" width="9.296875" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" customWidth="1"/>
+    <col min="8" max="8" width="11.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1800,7 +1856,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
         <v>144</v>
       </c>
@@ -1822,7 +1878,7 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A3" s="10" t="s">
         <v>145</v>
       </c>
@@ -1838,7 +1894,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A4" s="10" t="s">
         <v>146</v>
       </c>
@@ -1854,7 +1910,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A5" s="10" t="s">
         <v>147</v>
       </c>
@@ -1868,7 +1924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A6" s="10" t="s">
         <v>148</v>
       </c>
@@ -1886,7 +1942,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="10" t="s">
         <v>149</v>
       </c>
@@ -1902,7 +1958,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="10" t="s">
         <v>150</v>
       </c>
@@ -1918,7 +1974,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="10" t="s">
         <v>151</v>
       </c>
@@ -1935,7 +1991,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A10" s="10" t="s">
         <v>152</v>
       </c>
@@ -1950,7 +2006,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="10" t="s">
         <v>153</v>
       </c>
@@ -1958,7 +2014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A12" s="10" t="s">
         <v>154</v>
       </c>
@@ -1966,7 +2022,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A13" s="10" t="s">
         <v>155</v>
       </c>
@@ -1982,7 +2038,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A14" s="10" t="s">
         <v>155</v>
       </c>
@@ -2000,7 +2056,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="10" t="s">
         <v>156</v>
       </c>
@@ -2014,7 +2070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="10" t="s">
         <v>157</v>
       </c>
@@ -2036,7 +2092,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
         <v>17</v>
       </c>
@@ -2050,7 +2106,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="10" t="s">
         <v>111</v>
       </c>
@@ -2069,7 +2125,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="10" t="s">
         <v>112</v>
       </c>
@@ -2091,7 +2147,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="10" t="s">
         <v>135</v>
       </c>
@@ -2101,7 +2157,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="10" t="s">
         <v>113</v>
       </c>
@@ -2113,7 +2169,7 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="10" t="s">
         <v>114</v>
       </c>
@@ -2139,7 +2195,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="10" t="s">
         <v>115</v>
       </c>
@@ -2156,7 +2212,7 @@
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="10" t="s">
         <v>116</v>
       </c>
@@ -2177,7 +2233,7 @@
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A25" s="10" t="s">
         <v>117</v>
       </c>
@@ -2188,7 +2244,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A26" s="10" t="s">
         <v>118</v>
       </c>
@@ -2204,7 +2260,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A27" s="10" t="s">
         <v>119</v>
       </c>
@@ -2218,7 +2274,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A28" s="10" t="s">
         <v>19</v>
       </c>
@@ -2230,7 +2286,7 @@
       </c>
       <c r="I28" s="8"/>
     </row>
-    <row r="29" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A29" s="10" t="s">
         <v>120</v>
       </c>
@@ -2242,7 +2298,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A30" s="10" t="s">
         <v>121</v>
       </c>
@@ -2259,7 +2315,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A31" s="10" t="s">
         <v>140</v>
       </c>
@@ -2276,7 +2332,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:12" ht="18" x14ac:dyDescent="0.45">
       <c r="A32" s="10" t="s">
         <v>122</v>
       </c>
@@ -2292,7 +2348,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A33" s="10" t="s">
         <v>123</v>
       </c>
@@ -2317,7 +2373,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A34" s="10" t="s">
         <v>141</v>
       </c>
@@ -2334,7 +2390,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A35" s="10" t="s">
         <v>124</v>
       </c>
@@ -2353,7 +2409,7 @@
       <c r="F35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A36" s="10" t="s">
         <v>142</v>
       </c>
@@ -2372,7 +2428,7 @@
       <c r="F36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A37" s="10" t="s">
         <v>125</v>
       </c>
@@ -2400,7 +2456,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A38" s="10" t="s">
         <v>126</v>
       </c>
@@ -2428,7 +2484,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A39" s="10" t="s">
         <v>127</v>
       </c>
@@ -2442,7 +2498,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>143</v>
       </c>
@@ -2456,7 +2512,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A41" s="10" t="s">
         <v>22</v>
       </c>
@@ -2465,7 +2521,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A42" s="10" t="s">
         <v>23</v>
       </c>
@@ -2474,7 +2530,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>90</v>
       </c>
@@ -2494,43 +2550,44 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="10" t="s">
-        <v>128</v>
+    <row r="44" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-    </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A45" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" t="s">
-        <v>26</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>27</v>
@@ -2541,129 +2598,127 @@
       <c r="D46" t="s">
         <v>26</v>
       </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.45">
+      <c r="A48" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F48" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="9"/>
+      <c r="I48" s="3"/>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A49" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B49" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>32</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
+      <c r="I49" s="9"/>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A50" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A51" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B51" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>31</v>
+      <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="52" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A52" s="10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -2671,43 +2726,62 @@
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
     </row>
-    <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A53" s="10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.3">
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
+    <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.45">
+      <c r="A54" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+    </row>
+    <row r="55" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H53">
-    <sortCondition ref="A11:A53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H54">
+    <sortCondition ref="A11:A54"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/comment.xlsx
+++ b/comment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{481E7213-C6EC-44B2-B096-9C537337E363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B733C6B-10CA-4775-9341-A33987CFA5A0}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{481E7213-C6EC-44B2-B096-9C537337E363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED794663-10E6-4B15-8827-E96CFCF2D122}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C99B29C7-3A4C-4F85-8138-E5477A2FBA29}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="164">
   <si>
     <t>品番</t>
     <rPh sb="0" eb="2">
@@ -1340,6 +1340,20 @@
     </rPh>
     <rPh sb="13" eb="15">
       <t>ミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MC10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TIF期間限定品</t>
+    <rPh sb="3" eb="7">
+      <t>キカンゲンテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1817,13 +1831,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F89E10-74DD-4645-9643-023642A8D72D}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.8984375" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="14.3984375" customWidth="1"/>
+    <col min="3" max="3" width="31.296875" customWidth="1"/>
+    <col min="4" max="4" width="37.796875" customWidth="1"/>
     <col min="5" max="5" width="16.3984375" customWidth="1"/>
     <col min="6" max="6" width="9.296875" customWidth="1"/>
     <col min="7" max="7" width="9.19921875" customWidth="1"/>
@@ -2568,43 +2582,44 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.45">
-      <c r="A45" s="10" t="s">
-        <v>128</v>
+    <row r="45" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D45" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A46" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" t="s">
-        <v>26</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A47" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>27</v>
@@ -2615,129 +2630,127 @@
       <c r="D47" t="s">
         <v>26</v>
       </c>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:10" ht="18" x14ac:dyDescent="0.45">
       <c r="A48" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
       <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
     </row>
     <row r="49" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A49" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="9"/>
+      <c r="I49" s="3"/>
       <c r="J49" s="3"/>
     </row>
     <row r="50" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A50" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>32</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="I50" s="9"/>
       <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A51" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
     </row>
     <row r="52" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A52" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B52" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>31</v>
+      <c r="C52" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
     </row>
     <row r="53" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A53" s="10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -2747,41 +2760,60 @@
     </row>
     <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A54" s="10" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
-    <row r="55" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
+    <row r="55" spans="1:11" ht="18" x14ac:dyDescent="0.45">
+      <c r="A55" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+    </row>
+    <row r="56" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H54">
-    <sortCondition ref="A11:A54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H55">
+    <sortCondition ref="A11:A55"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
